--- a/Chapter/Figures/alt-text.xlsx
+++ b/Chapter/Figures/alt-text.xlsx
@@ -40,7 +40,8 @@
     <t xml:space="preserve">Figure 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Overview of the pangenome workflow described in this protocol. Top: the 31 HXB/BXH recombinant inbred rat strains, derived from SHR/OlaIpcv and BN-Lx/Cub progenitors, are sequenced and de novo assembled; assembly completeness is assessed with Compleasm (%BUSCOs). Upper middle: the PGGB pipeline constructs the pangenome graph through all-to-all alignment (WFMASH), graph induction (SEQWISH), graph normalization (SMOOTHXG), and redundancy removal (GFAFFIX). Lower middle: 1D visualization of the resulting pangenome graph (odgi viz), where each horizontal row represents a genome path and colored segments indicate node traversals. Bottom: downstream analyses including variant calling from graph snarls, read mapping with vg Giraffe, variant benchmarking (assembly evaluation and variant calling evaluation with precision, recall, and F1-score), and phenome-wide association study (PheWAS) linking variants to phenotypes.</t>
+    <t xml:space="preserve">Overview of the pangenome workflow described in this protocol. Top: the 31 HXB/BXH recombinant inbred rat strains, derived from SHR/OlaIpcv and BN-Lx/Cub progenitors, are sequenced and de novo assembled; assembly completeness is assessed with Compleasm (%BUSCOs). Upper middle: the PGGB pipeline constructs the pangenome graph through all-to-all alignment (WFMASH), graph induction (SEQWISH), graph normalization (SMOOTHXG), and redundancy removal (GFAFFIX). Lower middle: 1D visualization of the resulting pangenome graph (odgi viz), where each horizontal row represents a genome path and colored segments indicate node traversals. Bottom: downstream analyses including variant calling
+from graph snarls (illustrated with a two-genome bubble-graph schematic showing divergent paths through shared anchor nodes), read mapping with vg Giraffe (shown with short reads aligned to a similar bubble-graph), variant benchmarking (assembly evaluation and variant calling evaluation with precision, recall, and F1-score), and phenome-wide association study (PheWAS) linking variants to phenotypes.</t>
   </si>
   <si>
     <t xml:space="preserve">A vertical four-panel flowchart diagram. The top panel shows icons representing 31 rat genomes arranged in a row, with arrows pointing down to bar charts of assembly completeness scores. The upper-middle panel depicts the PGGB graph-construction pipeline as a linear sequence of four labeled processing boxes (WFMASH, SEQWISH, SMOOTHXG, GFAFFIX) connected by arrows from left to right. The lower-middle panel displays a dense, horizontally striped matrix visualization of the pangenome graph, with each colored horizontal band representing one genome path. The bottom panel branches into four output boxes arranged side by side: variant calling, read mapping, benchmarking metrics tables, and a PheWAS plot showing variant-phenotype associations.</t>
@@ -133,16 +134,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -341,36 +346,36 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="186.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="235.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Chapter/Figures/alt-text.xlsx
+++ b/Chapter/Figures/alt-text.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Overview of the pangenome workflow described in this protocol. *First (top)*: genome assemblies were generated from 10x Genomics Linked-Read sequencing of 31 HXB/BXH recombinant inbred strains derived from the parental SHR/OlaIpcv (H) and BN-Lx/Cub (B) strains; six representative strains (HXB23, BXH6, HXB21, SHROlaIpcv, BXH3, and BNLxCub) are shown. Assembly completeness is assessed with Compleasm (%BUSCOs). *Second (middle)*: chromosome-level pangenome graphs were built using PGGB; an example of the chr12 pangenome graph is shown, visualized with ODGI, where each horizontal colored line represents a haplotype and vertical white stripes indicate structural variation. *Third (bottom)*: downstream analyses including (i) variant calling from graph snarls (illustrated with a two-genome bubble-graph schematic showing divergent paths through shared anchor nodes); (ii) read mapping (shown with short reads aligned to a similar bubble-graph); (iii) variant benchmarking comparing the pangenome dataset against a genomic truth-set to capture pangenome-only, genomic-only, and shared variants, evaluated by precision, recall, and F1-score; (iv) phenome-wide association study (PheWAS) linking validated SNPs to phenotypes including blood glucose concentration and central nervous system traits via GeneNetwork; (v) structural variant (SV) validation using Nanopore adaptive sequencing to confirm a representative 82 bp insertion at chr12:1,942,010 across samples relative to the reference genome; (vi) SV interpretation showing haplotype-resolved allele frequencies across strains. A representative complex insertion of 82 bp in the Cd209c gene resolves into six haplotypes composed of seven variable blocks, of which four are observed fewer than two times.</t>
+          <t>Overview of the pangenome workflow described in this protocol. First (top): genome assemblies were generated from 10x Genomics Linked-Read sequencing of 31 HXB/BXH recombinant inbred strains derived from the parental SHR/OlaIpcv (H) and BN-Lx/Cub (B) strains; six representative strains, comprising the two parental lines and four RI strains (HXB23, BXH6, HXB21, SHROlaIpcv, BXH3, and BNLxCub), are shown. Assembly completeness is assessed with Compleasm (%BUSCOs). Second (middle): chromosome-level pangenome graphs were built using PGGB; an example of the chr12 pangenome graph is shown, visualized with ODGI, where each horizontal colored line represents a haplotype and vertical white stripes indicate structural variation. Third (bottom): downstream analyses including (i) variant calling from graph snarls (illustrated with a two-genome bubble-graph schematic showing divergent paths through shared anchor nodes); (ii) read mapping (shown with short reads aligned to a similar bubble-graph); (iii) variant benchmarking comparing the pangenome dataset against a genomic truth-set to capture pangenome-only, genomic-only, and shared variants, evaluated by precision, recall, and F1-score; (iv) phenome-wide association study (PheWAS) linking validated SNPs to phenotypes including blood glucose concentration and central nervous system traits via GeneNetwork; (v) structural variant (SV) validation using Nanopore adaptive sequencing to confirm a representative 82 bp insertion at chr12:1,942,010 across samples relative to the reference genome; (vi) SV interpretation showing haplotype-resolved allele frequencies across strains. A representative complex insertion of 82 bp in the Cd209c gene resolves into six haplotypes composed of seven variable blocks, of which four are observed fewer than two times.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
